--- a/65_Threshold_OUTPUT/direct_Q9ZFA4_Acidobacterium_capsulatum_ATCC_51196.xlsx
+++ b/65_Threshold_OUTPUT/direct_Q9ZFA4_Acidobacterium_capsulatum_ATCC_51196.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>CGAACAAAAACCGAACA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CGAACA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AAAAC&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.1105557776889244</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>AAAAA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AAAA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>AAAA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.7842862854858057</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AAAAA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9994002399040384</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>AACAAAAAC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;AAA&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9994002399040384</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>AACCGAAC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;CG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9994002399040384</v>
       </c>
     </row>
@@ -622,7 +682,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AACAA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -630,7 +690,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;C&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,7 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AACAAA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -659,7 +729,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CA&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,7 +760,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AACAAAA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -688,7 +768,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CAA&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,7 +799,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -717,7 +807,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;A&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -738,7 +838,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAAACCGAA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -746,7 +846,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AAACCG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -767,7 +877,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAAACCGAA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -775,7 +885,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AACCG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -796,7 +916,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAACCGAA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -804,7 +924,17 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;ACCG&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
